--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -85,31 +85,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
   </si>
   <si>
     <t>ANGEL</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>MARIA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -510,19 +534,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,22 +557,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>95.12</v>
+        <v>95</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,10 +586,10 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>35</v>
@@ -574,7 +598,7 @@
         <v>97.22</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -588,16 +612,16 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -705,16 +729,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -725,19 +752,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -751,16 +781,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -774,16 +807,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -797,16 +833,19 @@
         <v>37</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>37</v>
       </c>
-      <c r="E6">
-        <v>37</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -820,16 +859,19 @@
         <v>18</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>18</v>
       </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -882,10 +924,10 @@
         <v>34</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>2</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -905,22 +947,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>95.12</v>
+        <v>92.5</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,19 +976,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>97.22</v>
+        <v>88.89</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,19 +1002,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -998,7 +1040,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1024,7 +1066,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,22 +1108,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920374</v>
+        <v>22330051920303</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1089,25 +1131,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920221</v>
+        <v>22330051920312</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1118,10 +1160,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1130,6 +1172,75 @@
         <v>13</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920412</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920308</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920221</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
@@ -85,24 +85,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
     <t>QUESADA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
     <t>ANGEL</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -112,25 +115,22 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>MARIA</t>
   </si>
   <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>JARED DE JESUS</t>
   </si>
   <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>JOSSELIN GUADALUPE</t>
@@ -729,16 +729,16 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>91.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
         <v>8.1</v>
@@ -755,16 +755,16 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -781,19 +781,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1108,7 +1108,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920303</v>
+        <v>22330051920412</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920312</v>
+        <v>22330051920303</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1154,22 +1154,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920240</v>
+        <v>22330051920308</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1177,13 +1177,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920412</v>
+        <v>22330051920312</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
@@ -1195,30 +1195,30 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920308</v>
+        <v>20330051920240</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -97,12 +97,6 @@
     <t>QUESADA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -112,12 +106,6 @@
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
     <t>MIA NOEMI</t>
   </si>
   <si>
@@ -128,12 +116,6 @@
   </si>
   <si>
     <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
   </si>
 </sst>
 </file>
@@ -612,19 +594,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -807,19 +789,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1002,16 +984,16 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>8.699999999999999</v>
@@ -1076,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1114,10 +1096,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,10 +1119,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1163,7 +1145,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1183,10 +1165,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1195,52 +1177,6 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920240</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920221</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -85,18 +85,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>PANTOJA</t>
   </si>
   <si>
     <t>QUESADA</t>
   </si>
   <si>
+    <t>CADENA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
   </si>
   <si>
     <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
   </si>
   <si>
     <t>MIA NOEMI</t>
@@ -1058,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1090,7 +1096,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920412</v>
+        <v>22330051920423</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1099,13 +1105,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1113,7 +1119,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920303</v>
+        <v>22330051920412</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1122,7 +1128,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1136,16 +1142,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920308</v>
+        <v>22330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1159,16 +1165,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920312</v>
+        <v>22330051920308</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1177,6 +1183,29 @@
         <v>12</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920312</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -85,40 +85,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>PANTOJA</t>
   </si>
   <si>
     <t>QUESADA</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>CADENA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>OLGUIN</t>
   </si>
   <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>JARED DE JESUS</t>
@@ -1064,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1096,22 +1105,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920423</v>
+        <v>22330051920281</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1125,10 +1134,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,13 +1154,13 @@
         <v>22330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1168,13 +1177,13 @@
         <v>22330051920308</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1188,24 +1197,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
+        <v>22330051920423</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>22330051920312</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,54 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -924,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
         <v>8.199999999999999</v>
@@ -950,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -976,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1073,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1103,144 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920281</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920412</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920303</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920308</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920423</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920312</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
